--- a/backend/templates/template_cell_4g.xlsx
+++ b/backend/templates/template_cell_4g.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cell_4G" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cell_4G" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cell_4G'!$A$1:$AH$1</definedName>
@@ -36818,69 +36818,69 @@
   </sheetData>
   <autoFilter ref="A1:AH1"/>
   <dataValidations count="19">
-    <dataValidation sqref="A2:A1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$A$2:$A$35</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$B$2:$B$2995</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="H2:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VIP,VVIP"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
+    <dataValidation sqref="J2:J1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
       <formula1>8.33</formula1>
       <formula2>23.39</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
+    <dataValidation sqref="K2:K1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
       <formula1>102.14</formula1>
       <formula2>109.47</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Indoor,Outdoor"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Ericsson,Nokia,Huawei,ZTE,Samsung"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
+    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation sqref="O2:O1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
+    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>359</formula2>
     </dataValidation>
-    <dataValidation sqref="P2:P1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="Q2:Q1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="R2:R1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>'_Lookups'!$C$2:$C$67</formula1>
+    <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+      <formula1>'_Lookups'!$C$2:$C$68</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"2x2,4x4,8x8"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="AA2:AA1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"4G,2G/4G,3G/4G,2G/3G/4G,4G/5G"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="PCI phải trong khoảng 0 – 503" type="whole" operator="between">
+    <dataValidation sqref="AE2:AE1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="PCI phải trong khoảng 0 – 503" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>503</formula2>
     </dataValidation>
-    <dataValidation sqref="X2:X1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Cell max power không hợp lệ" error="Cell max power thường trong khoảng -30 đến 50 dBm" type="decimal" operator="between">
+    <dataValidation sqref="X2:X1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cell max power không hợp lệ" error="Cell max power thường trong khoảng -30 đến 50 dBm" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>50</formula2>
     </dataValidation>
@@ -37784,11 +37784,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TEST_ANTENNA</t>
+          <t>TONGYU|T0004M3V011</t>
         </is>
       </c>
     </row>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TEST_HUAWEI_AAU5613-1</t>
+          <t>TONGYU|TDJ-809018DM-65FT0</t>
         </is>
       </c>
     </row>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TONGYU|T0004M3V011</t>
+          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
         </is>
       </c>
     </row>
@@ -38718,7 +38718,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-809018DM-65FT0</t>
+          <t>TONGYU|TDJ-9018DM-65FT0</t>
         </is>
       </c>
     </row>
@@ -38730,7 +38730,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+          <t>TONGYU|TDJH-182018DE-65F</t>
         </is>
       </c>
     </row>
@@ -38742,7 +38742,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018DM-65FT0</t>
+          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38754,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TONGYU|TDJH-182018DE-65F</t>
+          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+          <t>test1</t>
         </is>
       </c>
     </row>
@@ -38786,6 +38786,11 @@
       <c r="B68" t="inlineStr">
         <is>
           <t>Phường Bình Hòa</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>test2</t>
         </is>
       </c>
     </row>

--- a/backend/templates/template_cell_4g.xlsx
+++ b/backend/templates/template_cell_4g.xlsx
@@ -36868,7 +36868,7 @@
       <formula2>30</formula2>
     </dataValidation>
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>'_Lookups'!$C$2:$C$68</formula1>
+      <formula1>'_Lookups'!$C$2:$C$83</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"2x2,4x4,8x8"</formula1>
@@ -38122,7 +38122,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GRENTECH|SGR-DTX-YC-18</t>
+          <t>ERICSSON|AIR3219B77U</t>
         </is>
       </c>
     </row>
@@ -38139,7 +38139,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HENGXIN|HX4W3319B2RNF</t>
+          <t>ERICSSON|AIR3265B41</t>
         </is>
       </c>
     </row>
@@ -38156,7 +38156,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HENGXIN|HXHH3820B2-EU</t>
+          <t>ERICSSON|AIR6419B41</t>
         </is>
       </c>
     </row>
@@ -38173,7 +38173,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HUAWEI|A19451811V01</t>
+          <t>ERICSSON|AIR6419B77D</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HUAWEI|A19451811V06</t>
+          <t>GRENTECH|SGR-DTX-YC-18</t>
         </is>
       </c>
     </row>
@@ -38207,7 +38207,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hengxin|HX4W6518DEF</t>
+          <t>HENGXIN|HX4W3319B2RNF</t>
         </is>
       </c>
     </row>
@@ -38224,7 +38224,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KATHREIN|739623</t>
+          <t>HENGXIN|HXHH3820B2-EU</t>
         </is>
       </c>
     </row>
@@ -38241,7 +38241,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KATHREIN|741 785</t>
+          <t>HUAWEI|A04040PA00v06</t>
         </is>
       </c>
     </row>
@@ -38258,7 +38258,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KATHREIN|741322</t>
+          <t>HUAWEI|A19451811V01</t>
         </is>
       </c>
     </row>
@@ -38275,7 +38275,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KATHREIN|742215</t>
+          <t>HUAWEI|A19451811V06</t>
         </is>
       </c>
     </row>
@@ -38292,7 +38292,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KATHREIN|742222V01</t>
+          <t>HUAWEI|AAU5336v</t>
         </is>
       </c>
     </row>
@@ -38309,7 +38309,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KATHREIN|742266V02</t>
+          <t>HUAWEI|AAU5356</t>
         </is>
       </c>
     </row>
@@ -38326,7 +38326,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KATHREIN|800 10492V01</t>
+          <t>HUAWEI|AAU5636m</t>
         </is>
       </c>
     </row>
@@ -38343,7 +38343,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KATHREIN|80010428</t>
+          <t>HUAWEI|AAU5636v</t>
         </is>
       </c>
     </row>
@@ -38360,7 +38360,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MOBI|MB3F-65-18DE10</t>
+          <t>HUAWEI|ADU4517R51v06</t>
         </is>
       </c>
     </row>
@@ -38377,7 +38377,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MOBI|MB900/1800-65-17/18DE10/8-C-VN</t>
+          <t>HUAWEI|AMB4519R47v06</t>
         </is>
       </c>
     </row>
@@ -38394,7 +38394,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NETOP|S-WAVE U-65-12D</t>
+          <t>Hengxin|HX4W6518DEF</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>POWERSTORM|C-BXH-65606580-M</t>
+          <t>KATHREIN|739623</t>
         </is>
       </c>
     </row>
@@ -38418,7 +38418,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PROSE|2G4W4XBF-27</t>
+          <t>KATHREIN|741 785</t>
         </is>
       </c>
     </row>
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROSE|S-WAVE EW_EW-65-14D-64F-O1</t>
+          <t>KATHREIN|741322</t>
         </is>
       </c>
     </row>
@@ -38442,7 +38442,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RFS|APX-906516L-0T0</t>
+          <t>KATHREIN|742215</t>
         </is>
       </c>
     </row>
@@ -38454,7 +38454,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RFS|APX86-906516L-T6</t>
+          <t>KATHREIN|742222V01</t>
         </is>
       </c>
     </row>
@@ -38466,7 +38466,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RFS|APXE20F-T6</t>
+          <t>KATHREIN|742266V02</t>
         </is>
       </c>
     </row>
@@ -38478,7 +38478,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ROSENBERGER|4WC-11M</t>
+          <t>KATHREIN|800 10492V01</t>
         </is>
       </c>
     </row>
@@ -38490,7 +38490,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ROSENBERGER|CA-D3W5V32F-SD01</t>
+          <t>KATHREIN|80010428</t>
         </is>
       </c>
     </row>
@@ -38502,7 +38502,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ROSENBERGER|G3WF-11M</t>
+          <t>MOBI|MB3F-65-18DE10</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 0809/U-65-18DV8</t>
+          <t>MOBI|MB900/1800-65-17/18DE10/8-C-VN</t>
         </is>
       </c>
     </row>
@@ -38526,7 +38526,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 0809/U/U-65-18DV8-B5</t>
+          <t>NETOP|S-WAVE U-65-12D</t>
         </is>
       </c>
     </row>
@@ -38538,7 +38538,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 09-65-18DV10-B3</t>
+          <t>NOKIA|AQHC</t>
         </is>
       </c>
     </row>
@@ -38550,7 +38550,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 1800-65-18DT6</t>
+          <t>NOKIA|AQQV</t>
         </is>
       </c>
     </row>
@@ -38562,7 +38562,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-10/12-LP</t>
+          <t>NOKIA|AVHA</t>
         </is>
       </c>
     </row>
@@ -38574,7 +38574,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-180-4/4.5-O2</t>
+          <t>NOKIA|AVQG</t>
         </is>
       </c>
     </row>
@@ -38586,7 +38586,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-OD-3-L500</t>
+          <t>POWERSTORM|C-BXH-65606580-M</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-14D-O1</t>
+          <t>PROSE|2G4W4XBF-27</t>
         </is>
       </c>
     </row>
@@ -38610,7 +38610,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-18DV2/12-VN1</t>
+          <t>PROSE|S-WAVE EW_EW-65-14D-64F-O1</t>
         </is>
       </c>
     </row>
@@ -38622,7 +38622,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-9D-O1</t>
+          <t>RFS|APX-906516L-0T0</t>
         </is>
       </c>
     </row>
@@ -38634,7 +38634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U-33-20DV10</t>
+          <t>RFS|APX86-906516L-T6</t>
         </is>
       </c>
     </row>
@@ -38646,7 +38646,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U-65-18DV10-B4</t>
+          <t>RFS|APXE20F-T6</t>
         </is>
       </c>
     </row>
@@ -38658,7 +38658,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U/U-33-20DV10-BS</t>
+          <t>ROSENBERGER|4WC-11M</t>
         </is>
       </c>
     </row>
@@ -38670,7 +38670,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U/U/U-33-21DT6-TS</t>
+          <t>ROSENBERGER|CA-D3W5V32F-SD01</t>
         </is>
       </c>
     </row>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TONGYU|T0004M3V011</t>
+          <t>ROSENBERGER|G3WF-11M</t>
         </is>
       </c>
     </row>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-809018DM-65FT0</t>
+          <t>ROSENBERGER|S-WAVE 0809/U-65-18DV8</t>
         </is>
       </c>
     </row>
@@ -38706,7 +38706,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+          <t>ROSENBERGER|S-WAVE 0809/U/U-65-18DV8-B5</t>
         </is>
       </c>
     </row>
@@ -38718,7 +38718,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018DM-65FT0</t>
+          <t>ROSENBERGER|S-WAVE 09-65-18DV10-B3</t>
         </is>
       </c>
     </row>
@@ -38730,7 +38730,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TONGYU|TDJH-182018DE-65F</t>
+          <t>ROSENBERGER|S-WAVE 1800-65-18DT6</t>
         </is>
       </c>
     </row>
@@ -38742,7 +38742,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+          <t>ROSENBERGER|S-WAVE 7FW-10/12-LP</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38754,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+          <t>ROSENBERGER|S-WAVE 7FW-180-4/4.5-O2</t>
         </is>
       </c>
     </row>
@@ -38766,7 +38766,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>ROSENBERGER|S-WAVE 7FW-OD-3-L500</t>
         </is>
       </c>
     </row>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-14D-O1</t>
         </is>
       </c>
     </row>
@@ -38790,7 +38790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-18DV2/12-VN1</t>
         </is>
       </c>
     </row>
@@ -38800,6 +38800,11 @@
           <t>Phường Bình Khê</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-9D-O1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -38807,6 +38812,11 @@
           <t>Phường Bình Kiến</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U-33-20DV10</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -38814,6 +38824,11 @@
           <t>Phường Bình Long</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U-65-18DV10-B4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -38821,6 +38836,11 @@
           <t>Phường Bình Lộc</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U/U-33-20DV10-BS</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -38828,6 +38848,11 @@
           <t>Phường Bình Lợi Trung</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U/U/U-33-21DT6-TS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -38835,6 +38860,11 @@
           <t>Phường Bình Minh</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TONGYU|T0004M3V011</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -38842,6 +38872,11 @@
           <t>Phường Bình Phú</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-809018DM-65FT0</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -38849,6 +38884,11 @@
           <t>Phường Bình Phước</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -38856,6 +38896,11 @@
           <t>Phường Bình Quới</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-9018DM-65FT0</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -38863,6 +38908,11 @@
           <t>Phường Bình Thuận</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJH-182018DE-65F</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -38870,6 +38920,11 @@
           <t>Phường Bình Thạnh</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
@@ -38877,6 +38932,11 @@
           <t>Phường Bình Thới</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
@@ -38884,6 +38944,11 @@
           <t>Phường Bình Thủy</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -38891,11 +38956,21 @@
           <t>Phường Bình Tiên</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>test1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
           <t>Phường Bình Trưng</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>test2</t>
         </is>
       </c>
     </row>

--- a/backend/templates/template_cell_4g.xlsx
+++ b/backend/templates/template_cell_4g.xlsx
@@ -36817,7 +36817,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AH1"/>
-  <dataValidations count="19">
+  <dataValidations count="14">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
@@ -36846,26 +36846,6 @@
     </dataValidation>
     <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Ericsson,Nokia,Huawei,ZTE,Samsung"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>999</formula2>
-    </dataValidation>
-    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>359</formula2>
-    </dataValidation>
-    <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
-    </dataValidation>
-    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
-    </dataValidation>
-    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
     </dataValidation>
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$C$2:$C$83</formula1>
@@ -37433,7 +37413,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Độ cao anten (m) – bắt buộc, số dương</t>
+          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -37450,7 +37430,7 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Góc phương vị – bắt buộc, trong 0–359</t>
+          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -37467,7 +37447,7 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Mechanical tilt – bắt buộc</t>
+          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -37484,7 +37464,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Electrical tilt – bắt buộc</t>
+          <t>Electrical tilt – bắt buộc (số hoặc chuỗi, vd: 4 hoặc IBC)</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -37501,7 +37481,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Tổng tilt = M-tilt + E-Tilt (tự tính hoặc để trống)</t>
+          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">

--- a/backend/templates/template_cell_4g.xlsx
+++ b/backend/templates/template_cell_4g.xlsx
@@ -584,21 +584,21 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="35" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -699,7 +699,7 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Baseband</t>
+          <t>Chung anten</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -734,42 +734,42 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Chung anten</t>
+          <t>EnodeB ID</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>EnodeB ID</t>
+          <t>EARFCN</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>EARFCN</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>PCI</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>PCI</t>
+          <t>Root Sequence ID</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Root Sequence ID</t>
+          <t>Bandwitdh</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Bandwitdh</t>
+          <t>ECI</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>ECI</t>
+          <t>OSS</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,11 @@
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>4G only</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="inlineStr">
@@ -836,17 +840,13 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4G</t>
-        </is>
-      </c>
+      <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
-      <c r="AE2" s="2" t="n">
+      <c r="AD2" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="AE2" s="2" t="n"/>
       <c r="AF2" s="2" t="n"/>
       <c r="AG2" s="2" t="n"/>
       <c r="AH2" s="2" t="n"/>
@@ -36817,7 +36817,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AH1"/>
-  <dataValidations count="14">
+  <dataValidations count="13">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
@@ -36850,13 +36850,10 @@
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$C$2:$C$83</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>"2x2,4x4,8x8"</formula1>
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+      <formula1>"4G only,3G4G,2G3G4G,4G5G,3G4G5G"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>"4G,2G/4G,3G/4G,2G/3G/4G,4G/5G"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE2:AE1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="PCI phải trong khoảng 0 – 503" type="whole" operator="between">
+    <dataValidation sqref="AD2:AD1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="PCI phải trong khoảng 0 – 503" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>503</formula2>
     </dataValidation>
@@ -36875,7 +36872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -37160,107 +37157,95 @@
       </c>
       <c r="C26" s="9" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa để trống</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>→ Tự động điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường). Ví dụ: HNIHKM44DI4DA → HNIHKM</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa đã có giá trị</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>→ Giữ nguyên giá trị đã nhập, KHÔNG tự động điền</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Không tìm thấy mã 6 ký tự</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>→ Tinh / Phuong xa để trống (không phải lỗi – các cột này KHÔNG bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MÔ TẢ CÁC CỘT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Tên cột</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Mô tả / Hướng dẫn</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Mien</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Miền: MB / MT / MN</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Tinh</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Tỉnh / Thành phố – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Phuong xa</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Phường / Xã – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Site Name</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Tên site – bắt buộc, phải khớp với site đã có</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Site Name Old</t>
+          <t>Tinh</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Tên site cũ – điền khi site vừa đổi tên</t>
+          <t>Tỉnh / Thành phố – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -37270,116 +37255,116 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Cell Name</t>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Phuong xa</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Tên cell – bắt buộc, duy nhất trong site</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
+          <t>Phường / Xã – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Site Name</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Tên site – bắt buộc, phải khớp với site đã có</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Cell Name Old</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Tên cell cũ – điền khi cell vừa đổi tên</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>Site Name Old</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Tên site cũ – điền khi site vừa đổi tên</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Cell Name</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Tên cell – bắt buộc, duy nhất trong site (vd: HNIHKM44DI4DA)</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Cell Name Old</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Tên cell cũ – điền khi cell vừa đổi tên</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
           <t>Cell VIP</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Mức độ VIP: VIP hoặc VVIP</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>MORAN</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>MORAN: VNPT HOST hoặc MBF HOST</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Latitude – phải trong 8.33–23.39</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Longitude – phải trong 102.14–109.47</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Vung phu song</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Vùng phủ sóng: Indoor hoặc Outdoor</t>
+          <t>MORAN: VNPT HOST hoặc MBF HOST</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -37391,12 +37376,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Lat</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Hãng thiết bị – bắt buộc, chọn từ danh sách</t>
+          <t>Latitude – phải trong 8.33–23.39</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -37408,12 +37393,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Do cao anten</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
+          <t>Longitude – phải trong 102.14–109.47</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -37423,31 +37408,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Azimuth</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Vung phu song</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>Vùng phủ sóng: Indoor hoặc Outdoor</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>M-tilt</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
+          <t>Hãng thiết bị – bắt buộc, chọn từ danh sách</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -37459,80 +37444,80 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
+          <t>Do cao anten</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Azimuth</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>M-tilt</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
           <t>E-Tilt</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Electrical tilt – bắt buộc (số hoặc chuỗi, vd: 4 hoặc IBC)</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Total Tilt</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Loai Anten</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Loại anten – chọn từ danh sách antenna</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Baseband</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Tên thiết bị baseband</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>Total Tilt</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Tên thiết bị RF</t>
+          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -37544,12 +37529,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Cell ID</t>
+          <t>Loai Anten</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Cell ID (chuỗi hoặc số)</t>
+          <t>Loại anten – chọn từ danh sách antenna</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -37561,12 +37546,12 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>MIMO</t>
+          <t>Chung anten</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Cấu hình MIMO: 2x2 / 4x4 / 8x8</t>
+          <t>Chung anten – chọn từ danh sách: 4G only, 3G4G, 2G3G4G, 4G5G, 3G4G5G</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -37578,12 +37563,12 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Cell max power (dBm)</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Công suất tối đa cell (dBm)</t>
+          <t>Tên thiết bị RF</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -37595,12 +37580,12 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>BBUname</t>
+          <t>Cell ID</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Tên BBU</t>
+          <t>Cell ID (chuỗi hoặc số)</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -37612,12 +37597,12 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Cell status (at dump time)</t>
+          <t>MIMO</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Trạng thái cell tại thời điểm dump</t>
+          <t>Cấu hình MIMO – nhập tự do (vd: 2x2, 4x4, 8x8, 32T32R)</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -37629,12 +37614,12 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>Chung anten</t>
+          <t>Cell max power (dBm)</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>Chung anten 4G: 4G / 2G/4G / 3G/4G / 2G/3G/4G / 4G/5G</t>
+          <t>Công suất tối đa cell (dBm)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -37646,12 +37631,12 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>EnodeB ID</t>
+          <t>BBUname</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>eNodeB ID</t>
+          <t>Tên BBU</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -37663,12 +37648,12 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>EARFCN</t>
+          <t>Cell status (at dump time)</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>E-UTRA Absolute Radio Frequency Channel Number</t>
+          <t>Trạng thái cell tại thời điểm dump</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -37680,12 +37665,12 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>EnodeB ID</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Tracking Area Code</t>
+          <t>eNodeB ID</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -37697,12 +37682,12 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>PCI</t>
+          <t>EARFCN</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>Physical Cell Identity 0–503</t>
+          <t>E-UTRA Absolute Radio Frequency Channel Number</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -37714,12 +37699,12 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Root Sequence ID</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Root Sequence Index</t>
+          <t>Tracking Area Code</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
@@ -37731,12 +37716,12 @@
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>Bandwitdh</t>
+          <t>PCI</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Bandwidth (MHz) – ví dụ: 5, 10, 15, 20</t>
+          <t>Physical Cell Identity 0–503</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -37748,15 +37733,66 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
+          <t>Root Sequence ID</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Root Sequence Index</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Bandwitdh</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Bandwidth (MHz) – ví dụ: 5, 10, 15, 20</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
           <t>ECI</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>E-UTRAN Cell Identifier</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>OSS</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Hệ thống OSS nguồn dữ liệu – nhập tự do</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
         </is>
@@ -37764,9 +37800,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>

--- a/backend/templates/template_cell_4g.xlsx
+++ b/backend/templates/template_cell_4g.xlsx
@@ -832,11 +832,7 @@
       </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>4x4</t>
-        </is>
-      </c>
+      <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
